--- a/Dowling/dowling-vs-valley-082826.xlsx
+++ b/Dowling/dowling-vs-valley-082826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R1a68842e840e4aa4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R8582139da9a84300"/>
   </sheets>
 </workbook>
 </file>
@@ -112,6 +112,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>R</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>DOUBLE WING OPEN</t>
   </si>
   <si>
@@ -203,6 +209,9 @@
   </si>
   <si>
     <t>6 TRAP</t>
+  </si>
+  <si>
+    <t>E-Alley</t>
   </si>
   <si>
     <t>TOSS</t>
@@ -465,17 +474,20 @@
       <c r="L3">
         <v>7</v>
       </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W3">
         <v>1</v>
@@ -504,7 +516,7 @@
         <v>-20</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
         <v>30</v>
@@ -521,17 +533,20 @@
       <c r="L4">
         <v>7</v>
       </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -557,34 +572,34 @@
         <v>-24</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -610,7 +625,7 @@
         <v>-34</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
@@ -627,17 +642,20 @@
       <c r="L6">
         <v>7</v>
       </c>
+      <c r="M6" t="s">
+        <v>38</v>
+      </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -666,10 +684,10 @@
         <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>-3</v>
@@ -683,17 +701,20 @@
       <c r="N7">
         <v>0</v>
       </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -722,13 +743,13 @@
         <v>-31</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J8">
         <v>-4</v>
@@ -740,19 +761,19 @@
         <v>6</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -781,13 +802,13 @@
         <v>-27</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X9">
         <v>1</v>
@@ -801,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -813,7 +834,7 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -830,14 +851,17 @@
       <c r="L10">
         <v>6</v>
       </c>
+      <c r="M10" t="s">
+        <v>33</v>
+      </c>
       <c r="R10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -851,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -863,7 +887,7 @@
         <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
@@ -880,14 +904,17 @@
       <c r="L11">
         <v>6</v>
       </c>
+      <c r="M11" t="s">
+        <v>38</v>
+      </c>
       <c r="R11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -901,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -913,7 +940,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
         <v>30</v>
@@ -930,14 +957,17 @@
       <c r="L12">
         <v>6</v>
       </c>
+      <c r="M12" t="s">
+        <v>33</v>
+      </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -951,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -963,7 +993,7 @@
         <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
@@ -981,10 +1011,10 @@
         <v>8</v>
       </c>
       <c r="S13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -998,7 +1028,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1010,7 +1040,7 @@
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
@@ -1022,19 +1052,19 @@
         <v>-1</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
       <c r="R14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -1048,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1063,13 +1093,13 @@
         <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -1083,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1107,19 +1137,19 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L16">
         <v>7</v>
       </c>
       <c r="R16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -1157,25 +1187,28 @@
         <v>8</v>
       </c>
       <c r="K17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
+      <c r="M17" t="s">
+        <v>38</v>
+      </c>
       <c r="R17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X17">
         <v>2</v>
@@ -1213,22 +1246,25 @@
         <v>3</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
+      <c r="M18" t="s">
+        <v>66</v>
+      </c>
       <c r="R18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -1257,13 +1293,13 @@
         <v>-37</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -1275,16 +1311,16 @@
         <v>6</v>
       </c>
       <c r="R19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="T19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W19">
         <v>3</v>
@@ -1313,7 +1349,7 @@
         <v>-36</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -1325,22 +1361,25 @@
         <v>9</v>
       </c>
       <c r="K20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
+      <c r="M20" t="s">
+        <v>29</v>
+      </c>
       <c r="R20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W20">
         <v>3</v>
@@ -1386,20 +1425,23 @@
       <c r="L21">
         <v>7</v>
       </c>
+      <c r="M21" t="s">
+        <v>66</v>
+      </c>
       <c r="R21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W21">
         <v>3</v>
@@ -1428,13 +1470,13 @@
         <v>-41</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X22">
         <v>2</v>
@@ -1448,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1460,13 +1502,13 @@
         <v>-22</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J23">
         <v>28</v>
@@ -1480,14 +1522,17 @@
       <c r="N23">
         <v>11</v>
       </c>
+      <c r="O23">
+        <v>5</v>
+      </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X23">
         <v>2</v>
@@ -1501,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1525,16 +1570,16 @@
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L24">
         <v>7</v>
       </c>
       <c r="R24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X24">
         <v>2</v>
@@ -1548,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1560,7 +1605,7 @@
         <v>48</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s">
         <v>30</v>
@@ -1578,13 +1623,13 @@
         <v>7</v>
       </c>
       <c r="R25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X25">
         <v>2</v>
@@ -1598,7 +1643,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1610,7 +1655,7 @@
         <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -1628,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="U26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X26">
         <v>2</v>
@@ -1642,7 +1687,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1654,19 +1699,19 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -1674,14 +1719,17 @@
       <c r="N27">
         <v>38</v>
       </c>
+      <c r="O27">
+        <v>7</v>
+      </c>
       <c r="R27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X27">
         <v>2</v>
@@ -1695,7 +1743,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1707,7 +1755,7 @@
         <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -1719,19 +1767,19 @@
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
       <c r="R28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="U28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X28">
         <v>2</v>
@@ -1745,7 +1793,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1757,7 +1805,7 @@
         <v>37</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
         <v>30</v>
@@ -1769,16 +1817,16 @@
         <v>-3</v>
       </c>
       <c r="K29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L29">
         <v>6</v>
       </c>
       <c r="R29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X29">
         <v>2</v>
@@ -1804,10 +1852,10 @@
         <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s">
         <v>28</v>
@@ -1853,20 +1901,23 @@
       <c r="L31">
         <v>7</v>
       </c>
+      <c r="M31" t="s">
+        <v>38</v>
+      </c>
       <c r="R31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="T31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -1898,10 +1949,10 @@
         <v>26</v>
       </c>
       <c r="H32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I32" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1915,20 +1966,23 @@
       <c r="N32">
         <v>11</v>
       </c>
+      <c r="O32">
+        <v>6</v>
+      </c>
       <c r="R32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="X32">
         <v>3</v>
@@ -1957,10 +2011,10 @@
         <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1974,17 +2028,20 @@
       <c r="N33">
         <v>11</v>
       </c>
+      <c r="O33">
+        <v>5</v>
+      </c>
       <c r="R33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T33" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X33">
         <v>3</v>
@@ -2013,10 +2070,10 @@
         <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q34">
         <v>6</v>
@@ -2033,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2045,13 +2102,13 @@
         <v>-48</v>
       </c>
       <c r="G35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J35">
         <v>11</v>
@@ -2065,14 +2122,17 @@
       <c r="N35">
         <v>4</v>
       </c>
+      <c r="O35">
+        <v>2</v>
+      </c>
       <c r="R35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X35">
         <v>3</v>
@@ -2086,7 +2146,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2116,13 +2176,13 @@
         <v>6</v>
       </c>
       <c r="R36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X36">
         <v>3</v>
@@ -2136,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2148,7 +2208,7 @@
         <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H37" t="s">
         <v>30</v>
@@ -2160,19 +2220,19 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
       <c r="R37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S37" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X37">
         <v>3</v>
@@ -2186,7 +2246,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -2198,19 +2258,19 @@
         <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -2218,14 +2278,17 @@
       <c r="N38">
         <v>0</v>
       </c>
+      <c r="O38">
+        <v>2</v>
+      </c>
       <c r="R38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X38">
         <v>3</v>
@@ -2254,10 +2317,10 @@
         <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J39">
         <v>2</v>
@@ -2269,16 +2332,16 @@
         <v>6</v>
       </c>
       <c r="R39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S39" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X39">
         <v>4</v>
@@ -2321,20 +2384,23 @@
       <c r="L40">
         <v>8</v>
       </c>
+      <c r="M40" t="s">
+        <v>38</v>
+      </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T40" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="X40">
         <v>4</v>
@@ -2363,10 +2429,10 @@
         <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2380,17 +2446,20 @@
       <c r="N41">
         <v>13</v>
       </c>
+      <c r="O41">
+        <v>5</v>
+      </c>
       <c r="R41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T41" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -2422,10 +2491,10 @@
         <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I42" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X42">
         <v>4</v>
@@ -2439,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2454,10 +2523,10 @@
         <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -2471,14 +2540,17 @@
       <c r="N43">
         <v>5</v>
       </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
       <c r="R43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S43" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X43">
         <v>4</v>
@@ -2492,7 +2564,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -2504,7 +2576,7 @@
         <v>-47</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s">
         <v>30</v>
@@ -2516,19 +2588,19 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L44">
         <v>7</v>
       </c>
       <c r="R44" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X44">
         <v>4</v>
@@ -2542,7 +2614,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -2554,13 +2626,13 @@
         <v>-47</v>
       </c>
       <c r="G45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H45" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I45" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J45">
         <v>53</v>
@@ -2574,11 +2646,14 @@
       <c r="N45">
         <v>0</v>
       </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X45">
         <v>4</v>
@@ -2604,10 +2679,10 @@
         <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X46">
         <v>4</v>
@@ -2656,7 +2731,7 @@
         <v>-20</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H48" t="s">
         <v>30</v>
@@ -2673,17 +2748,20 @@
       <c r="L48">
         <v>6</v>
       </c>
+      <c r="M48" t="s">
+        <v>38</v>
+      </c>
       <c r="R48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T48" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W48">
         <v>3</v>
@@ -2712,13 +2790,13 @@
         <v>-18</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H49" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I49" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -2732,17 +2810,20 @@
       <c r="N49">
         <v>0</v>
       </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
       <c r="R49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T49" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W49">
         <v>3</v>
@@ -2771,13 +2852,13 @@
         <v>-18</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J50">
         <v>7</v>
@@ -2791,17 +2872,20 @@
       <c r="N50">
         <v>5</v>
       </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
       <c r="R50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W50">
         <v>6</v>
@@ -2830,13 +2914,13 @@
         <v>-25</v>
       </c>
       <c r="G51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I51" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X51">
         <v>4</v>
@@ -2850,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2862,7 +2946,7 @@
         <v>-40</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H52" t="s">
         <v>30</v>
@@ -2874,16 +2958,16 @@
         <v>3</v>
       </c>
       <c r="K52" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
       <c r="R52" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X52">
         <v>5</v>
@@ -2897,7 +2981,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -2909,7 +2993,7 @@
         <v>-43</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H53" t="s">
         <v>30</v>
@@ -2921,19 +3005,19 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L53">
         <v>7</v>
       </c>
       <c r="R53" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X53">
         <v>5</v>
@@ -2947,7 +3031,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -2959,13 +3043,13 @@
         <v>-45</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I54" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J54">
         <v>11</v>
@@ -2979,11 +3063,14 @@
       <c r="N54">
         <v>11</v>
       </c>
+      <c r="O54">
+        <v>6</v>
+      </c>
       <c r="R54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X54">
         <v>5</v>
@@ -2997,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3009,13 +3096,13 @@
         <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I55" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J55">
         <v>41</v>
@@ -3029,14 +3116,17 @@
       <c r="N55">
         <v>36</v>
       </c>
+      <c r="O55">
+        <v>7</v>
+      </c>
       <c r="R55" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S55" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X55">
         <v>5</v>
@@ -3050,7 +3140,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3062,13 +3152,13 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
         <v>30</v>
       </c>
       <c r="I56" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J56">
         <v>3</v>
@@ -3080,13 +3170,13 @@
         <v>9</v>
       </c>
       <c r="R56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S56" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X56">
         <v>5</v>
@@ -3112,10 +3202,10 @@
         <v>26</v>
       </c>
       <c r="H57" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X57">
         <v>5</v>
@@ -3144,7 +3234,7 @@
         <v>27</v>
       </c>
       <c r="I58" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q58">
         <v>22</v>
@@ -3185,22 +3275,25 @@
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L59">
         <v>5</v>
       </c>
+      <c r="M59" t="s">
+        <v>33</v>
+      </c>
       <c r="R59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T59" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W59">
         <v>6</v>
@@ -3232,7 +3325,7 @@
         <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s">
         <v>28</v>
@@ -3249,7 +3342,7 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3261,7 +3354,7 @@
         <v>-20</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61" t="s">
         <v>30</v>
@@ -3279,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="R61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S61" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X61">
         <v>4</v>
@@ -3299,7 +3392,7 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3311,7 +3404,7 @@
         <v>-29</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
         <v>30</v>
@@ -3323,19 +3416,19 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L62">
         <v>8</v>
       </c>
       <c r="R62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S62" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X62">
         <v>4</v>
@@ -3349,7 +3442,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -3361,7 +3454,7 @@
         <v>-29</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
         <v>30</v>
@@ -3379,13 +3472,13 @@
         <v>7</v>
       </c>
       <c r="R63" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X63">
         <v>4</v>
@@ -3399,7 +3492,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3411,7 +3504,7 @@
         <v>-31</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
         <v>30</v>
@@ -3429,13 +3522,13 @@
         <v>7</v>
       </c>
       <c r="R64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S64" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X64">
         <v>4</v>
@@ -3449,7 +3542,7 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3461,7 +3554,7 @@
         <v>-35</v>
       </c>
       <c r="G65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H65" t="s">
         <v>30</v>
@@ -3479,13 +3572,13 @@
         <v>7</v>
       </c>
       <c r="R65" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S65" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X65">
         <v>4</v>
@@ -3499,7 +3592,7 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -3511,7 +3604,7 @@
         <v>-38</v>
       </c>
       <c r="G66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H66" t="s">
         <v>30</v>
@@ -3523,13 +3616,13 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L66">
         <v>7</v>
       </c>
       <c r="U66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X66">
         <v>4</v>
@@ -3558,10 +3651,10 @@
         <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I67" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J67">
         <v>-5</v>
@@ -3590,13 +3683,13 @@
         <v>-34</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I68" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="X68">
         <v>4</v>
@@ -3622,7 +3715,7 @@
         <v>-26</v>
       </c>
       <c r="G69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H69" t="s">
         <v>30</v>
@@ -3639,20 +3732,23 @@
       <c r="L69">
         <v>7</v>
       </c>
+      <c r="M69" t="s">
+        <v>33</v>
+      </c>
       <c r="R69" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S69" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T69" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W69" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X69">
         <v>6</v>
@@ -3678,7 +3774,7 @@
         <v>-27</v>
       </c>
       <c r="G70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H70" t="s">
         <v>30</v>
@@ -3690,25 +3786,28 @@
         <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L70">
         <v>6</v>
       </c>
+      <c r="M70" t="s">
+        <v>66</v>
+      </c>
       <c r="R70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S70" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T70" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W70" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X70">
         <v>6</v>
@@ -3734,7 +3833,7 @@
         <v>-40</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H71" t="s">
         <v>30</v>
@@ -3751,17 +3850,20 @@
       <c r="L71">
         <v>7</v>
       </c>
+      <c r="M71" t="s">
+        <v>33</v>
+      </c>
       <c r="R71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S71" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="T71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W71">
         <v>3</v>
@@ -3790,7 +3892,7 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H72" t="s">
         <v>30</v>
@@ -3807,17 +3909,20 @@
       <c r="L72">
         <v>7</v>
       </c>
+      <c r="M72" t="s">
+        <v>66</v>
+      </c>
       <c r="R72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S72" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T72" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W72">
         <v>3</v>
@@ -3849,10 +3954,10 @@
         <v>26</v>
       </c>
       <c r="H73" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I73" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J73">
         <v>-9</v>
@@ -3864,16 +3969,16 @@
         <v>7</v>
       </c>
       <c r="R73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T73" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W73">
         <v>6</v>
@@ -3905,10 +4010,10 @@
         <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I74" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X74">
         <v>6</v>
@@ -3922,7 +4027,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3934,7 +4039,7 @@
         <v>-34</v>
       </c>
       <c r="G75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H75" t="s">
         <v>30</v>
@@ -3955,13 +4060,13 @@
         <v>0</v>
       </c>
       <c r="R75" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S75" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X75">
         <v>5</v>
@@ -3975,7 +4080,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3999,19 +4104,19 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L76">
         <v>7</v>
       </c>
       <c r="R76" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S76" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X76">
         <v>5</v>
@@ -4025,7 +4130,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -4040,10 +4145,10 @@
         <v>26</v>
       </c>
       <c r="H77" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J77">
         <v>30</v>
@@ -4057,14 +4162,17 @@
       <c r="N77">
         <v>27</v>
       </c>
+      <c r="O77">
+        <v>9</v>
+      </c>
       <c r="R77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S77" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X77">
         <v>5</v>
@@ -4078,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4090,7 +4198,7 @@
         <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s">
         <v>30</v>
@@ -4108,13 +4216,13 @@
         <v>7</v>
       </c>
       <c r="R78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X78">
         <v>5</v>
@@ -4128,7 +4236,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4158,13 +4266,13 @@
         <v>7</v>
       </c>
       <c r="R79" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X79">
         <v>5</v>
@@ -4178,7 +4286,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4208,13 +4316,13 @@
         <v>7</v>
       </c>
       <c r="R80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S80" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X80">
         <v>5</v>
@@ -4228,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -4240,7 +4348,7 @@
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H81" t="s">
         <v>30</v>
@@ -4252,19 +4360,19 @@
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L81">
         <v>7</v>
       </c>
       <c r="R81" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S81" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X81">
         <v>5</v>
@@ -4278,7 +4386,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -4290,7 +4398,7 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H82" t="s">
         <v>30</v>
@@ -4308,13 +4416,13 @@
         <v>7</v>
       </c>
       <c r="R82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S82" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X82">
         <v>5</v>
@@ -4328,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4340,7 +4448,7 @@
         <v>4</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H83" t="s">
         <v>30</v>
@@ -4358,13 +4466,13 @@
         <v>8</v>
       </c>
       <c r="R83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S83" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X83">
         <v>5</v>
@@ -4378,7 +4486,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4396,7 +4504,7 @@
         <v>30</v>
       </c>
       <c r="I84" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -4408,13 +4516,13 @@
         <v>9</v>
       </c>
       <c r="R84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="U84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X84">
         <v>5</v>
@@ -4440,10 +4548,10 @@
         <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I85" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X85">
         <v>5</v>
@@ -4472,7 +4580,7 @@
         <v>27</v>
       </c>
       <c r="I86" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q86">
         <v>17</v>
@@ -4501,19 +4609,19 @@
         <v>-21</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H87" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I87" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J87">
         <v>14</v>
       </c>
       <c r="K87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L87">
         <v>7</v>
@@ -4521,20 +4629,23 @@
       <c r="N87">
         <v>11</v>
       </c>
+      <c r="O87">
+        <v>5</v>
+      </c>
       <c r="R87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S87" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X87">
         <v>5</v>
@@ -4560,7 +4671,7 @@
         <v>-35</v>
       </c>
       <c r="G88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H88" t="s">
         <v>30</v>
@@ -4577,17 +4688,20 @@
       <c r="L88">
         <v>7</v>
       </c>
+      <c r="M88" t="s">
+        <v>38</v>
+      </c>
       <c r="R88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X88">
         <v>5</v>
@@ -4601,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4633,7 +4747,7 @@
         <v>-38</v>
       </c>
       <c r="G90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H90" t="s">
         <v>30</v>
@@ -4650,20 +4764,23 @@
       <c r="L90">
         <v>6</v>
       </c>
+      <c r="M90" t="s">
+        <v>38</v>
+      </c>
       <c r="R90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S90" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T90" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W90" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X90">
         <v>5</v>
@@ -4689,13 +4806,13 @@
         <v>-38</v>
       </c>
       <c r="G91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H91" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I91" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4709,17 +4826,20 @@
       <c r="N91">
         <v>13</v>
       </c>
+      <c r="O91">
+        <v>4</v>
+      </c>
       <c r="R91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S91" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T91" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W91">
         <v>6</v>
@@ -4748,13 +4868,13 @@
         <v>-38</v>
       </c>
       <c r="G92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I92" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X92">
         <v>5</v>
@@ -4768,7 +4888,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4792,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L93">
         <v>7</v>
@@ -4801,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="R93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S93" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X93">
         <v>7</v>
@@ -4821,7 +4941,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4845,19 +4965,19 @@
         <v>3</v>
       </c>
       <c r="K94" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L94">
         <v>7</v>
       </c>
       <c r="R94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X94">
         <v>7</v>
@@ -4871,7 +4991,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -4883,13 +5003,13 @@
         <v>-36</v>
       </c>
       <c r="G95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H95" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I95" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J95">
         <v>8</v>
@@ -4903,14 +5023,17 @@
       <c r="N95">
         <v>9</v>
       </c>
+      <c r="O95">
+        <v>3</v>
+      </c>
       <c r="R95" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S95" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="U95" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X95">
         <v>7</v>
@@ -4924,7 +5047,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4936,7 +5059,7 @@
         <v>-44</v>
       </c>
       <c r="G96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H96" t="s">
         <v>30</v>
@@ -4948,19 +5071,19 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L96">
         <v>7</v>
       </c>
       <c r="R96" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X96">
         <v>7</v>
@@ -4974,7 +5097,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -4986,7 +5109,7 @@
         <v>-46</v>
       </c>
       <c r="G97" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H97" t="s">
         <v>30</v>
@@ -4998,19 +5121,19 @@
         <v>-2</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L97">
         <v>7</v>
       </c>
       <c r="R97" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S97" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="U97" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X97">
         <v>7</v>
@@ -5024,7 +5147,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -5036,19 +5159,19 @@
         <v>-44</v>
       </c>
       <c r="G98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H98" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I98" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L98">
         <v>7</v>
@@ -5056,14 +5179,17 @@
       <c r="N98">
         <v>41</v>
       </c>
+      <c r="O98">
+        <v>9</v>
+      </c>
       <c r="R98" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S98" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X98">
         <v>7</v>
@@ -5089,13 +5215,13 @@
         <v>-44</v>
       </c>
       <c r="G99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H99" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I99" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X99">
         <v>7</v>
@@ -5121,40 +5247,43 @@
         <v>-31</v>
       </c>
       <c r="G100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I100" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J100">
         <v>5</v>
       </c>
       <c r="K100" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L100">
         <v>6</v>
       </c>
       <c r="N100">
         <v>3</v>
+      </c>
+      <c r="O100">
+        <v>2</v>
       </c>
       <c r="Q100">
         <v>0</v>
       </c>
       <c r="R100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S100" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T100" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W100">
         <v>3</v>
@@ -5186,31 +5315,31 @@
         <v>26</v>
       </c>
       <c r="H101" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I101" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J101">
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
       <c r="R101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S101" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="T101" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X101">
         <v>6</v>
@@ -5236,19 +5365,19 @@
         <v>-39</v>
       </c>
       <c r="G102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H102" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I102" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J102">
         <v>16</v>
       </c>
       <c r="K102" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L102">
         <v>7</v>
@@ -5256,17 +5385,20 @@
       <c r="N102">
         <v>13</v>
       </c>
+      <c r="O102">
+        <v>4</v>
+      </c>
       <c r="R102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S102" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T102" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="U102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W102">
         <v>3</v>
@@ -5295,13 +5427,13 @@
         <v>45</v>
       </c>
       <c r="G103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H103" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I103" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5315,17 +5447,20 @@
       <c r="N103">
         <v>0</v>
       </c>
+      <c r="O103">
+        <v>3</v>
+      </c>
       <c r="R103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S103" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T103" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U103" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W103">
         <v>3</v>
@@ -5354,7 +5489,7 @@
         <v>45</v>
       </c>
       <c r="G104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H104" t="s">
         <v>30</v>
@@ -5366,22 +5501,25 @@
         <v>5</v>
       </c>
       <c r="K104" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L104">
         <v>7</v>
       </c>
+      <c r="M104" t="s">
+        <v>33</v>
+      </c>
       <c r="R104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S104" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="T104" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="U104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W104">
         <v>3</v>
@@ -5410,7 +5548,7 @@
         <v>40</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
         <v>30</v>
@@ -5422,25 +5560,28 @@
         <v>7</v>
       </c>
       <c r="K105" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L105">
         <v>8</v>
       </c>
+      <c r="M105" t="s">
+        <v>38</v>
+      </c>
       <c r="R105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S105" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T105" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W105" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="X105">
         <v>6</v>
@@ -5469,10 +5610,10 @@
         <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I106" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -5486,17 +5627,20 @@
       <c r="N106">
         <v>33</v>
       </c>
+      <c r="O106">
+        <v>7</v>
+      </c>
       <c r="R106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S106" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T106" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W106">
         <v>6</v>
@@ -5525,13 +5669,13 @@
         <v>33</v>
       </c>
       <c r="G107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H107" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I107" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J107">
         <v>-3</v>
@@ -5543,16 +5687,16 @@
         <v>7</v>
       </c>
       <c r="R107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S107" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="T107" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="U107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W107">
         <v>3</v>
@@ -5569,7 +5713,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5593,19 +5737,19 @@
         <v>3</v>
       </c>
       <c r="K108" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L108">
         <v>7</v>
       </c>
       <c r="R108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S108" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X108">
         <v>8</v>
@@ -5619,7 +5763,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5631,7 +5775,7 @@
         <v>-39</v>
       </c>
       <c r="G109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H109" t="s">
         <v>30</v>
@@ -5643,19 +5787,19 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L109">
         <v>7</v>
       </c>
       <c r="R109" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S109" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X109">
         <v>8</v>
@@ -5669,7 +5813,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5681,7 +5825,7 @@
         <v>-41</v>
       </c>
       <c r="G110" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H110" t="s">
         <v>30</v>
@@ -5693,19 +5837,19 @@
         <v>-1</v>
       </c>
       <c r="K110" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L110">
         <v>7</v>
       </c>
       <c r="R110" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S110" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U110" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X110">
         <v>8</v>
@@ -5734,10 +5878,10 @@
         <v>26</v>
       </c>
       <c r="H111" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I111" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q111">
         <v>15</v>
@@ -5766,37 +5910,40 @@
         <v>-42</v>
       </c>
       <c r="G112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H112" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I112" t="s">
+        <v>47</v>
+      </c>
+      <c r="J112">
+        <v>7</v>
+      </c>
+      <c r="K112" t="s">
+        <v>43</v>
+      </c>
+      <c r="L112">
+        <v>7</v>
+      </c>
+      <c r="N112">
+        <v>6</v>
+      </c>
+      <c r="O112">
+        <v>1</v>
+      </c>
+      <c r="R112" t="s">
+        <v>37</v>
+      </c>
+      <c r="S112" t="s">
+        <v>44</v>
+      </c>
+      <c r="T112" t="s">
         <v>45</v>
       </c>
-      <c r="J112">
-        <v>7</v>
-      </c>
-      <c r="K112" t="s">
-        <v>41</v>
-      </c>
-      <c r="L112">
-        <v>7</v>
-      </c>
-      <c r="N112">
-        <v>6</v>
-      </c>
-      <c r="R112" t="s">
-        <v>36</v>
-      </c>
-      <c r="S112" t="s">
-        <v>42</v>
-      </c>
-      <c r="T112" t="s">
-        <v>43</v>
-      </c>
       <c r="U112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W112">
         <v>3</v>
@@ -5825,19 +5972,19 @@
         <v>-49</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H113" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I113" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J113">
         <v>10</v>
       </c>
       <c r="K113" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L113">
         <v>6</v>
@@ -5845,20 +5992,23 @@
       <c r="N113">
         <v>2</v>
       </c>
+      <c r="O113">
+        <v>3</v>
+      </c>
       <c r="R113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S113" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T113" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="U113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W113" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X113">
         <v>7</v>
@@ -5884,19 +6034,19 @@
         <v>41</v>
       </c>
       <c r="G114" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H114" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I114" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J114">
         <v>10</v>
       </c>
       <c r="K114" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L114">
         <v>6</v>
@@ -5904,20 +6054,23 @@
       <c r="N114">
         <v>11</v>
       </c>
+      <c r="O114">
+        <v>4</v>
+      </c>
       <c r="R114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T114" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W114" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X114">
         <v>7</v>
@@ -5943,25 +6096,25 @@
         <v>31</v>
       </c>
       <c r="G115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H115" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I115" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J115">
         <v>6</v>
       </c>
       <c r="K115" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R115" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="X115">
         <v>7</v>
@@ -5987,13 +6140,13 @@
         <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H116" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I116" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J116">
         <v>-4</v>
@@ -6005,19 +6158,19 @@
         <v>5</v>
       </c>
       <c r="R116" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S116" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T116" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U116" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W116" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X116">
         <v>7</v>
@@ -6046,10 +6199,10 @@
         <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I117" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6063,17 +6216,20 @@
       <c r="N117">
         <v>12</v>
       </c>
+      <c r="O117">
+        <v>4</v>
+      </c>
       <c r="R117" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S117" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T117" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U117" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W117">
         <v>3</v>
@@ -6105,7 +6261,7 @@
         <v>26</v>
       </c>
       <c r="I118" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J118">
         <v>-5</v>
@@ -6114,10 +6270,10 @@
         <v>32</v>
       </c>
       <c r="R118" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S118" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="W118">
         <v>6</v>
@@ -6146,13 +6302,13 @@
         <v>34</v>
       </c>
       <c r="G119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H119" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I119" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6166,17 +6322,20 @@
       <c r="N119">
         <v>6</v>
       </c>
+      <c r="O119">
+        <v>1</v>
+      </c>
       <c r="R119" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S119" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T119" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W119">
         <v>6</v>
@@ -6193,7 +6352,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -6205,7 +6364,7 @@
         <v>-34</v>
       </c>
       <c r="G120" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H120" t="s">
         <v>30</v>
@@ -6217,19 +6376,19 @@
         <v>-3</v>
       </c>
       <c r="K120" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L120">
         <v>7</v>
       </c>
       <c r="R120" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S120" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X120">
         <v>9</v>
@@ -6243,7 +6402,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6267,19 +6426,19 @@
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L121">
         <v>7</v>
       </c>
       <c r="R121" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S121" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U121" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X121">
         <v>9</v>

--- a/Dowling/dowling-vs-valley-082826.xlsx
+++ b/Dowling/dowling-vs-valley-082826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R8582139da9a84300"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R26401007a2c04992"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -115,6 +127,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>MIAMI</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
@@ -166,6 +184,9 @@
     <t>Sack</t>
   </si>
   <si>
+    <t>FLEX TANGO</t>
+  </si>
+  <si>
     <t>ACE</t>
   </si>
   <si>
@@ -181,6 +202,9 @@
     <t>O</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -193,9 +217,15 @@
     <t>IOWA</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>UCONN</t>
   </si>
   <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
     <t>WASHINGTON</t>
   </si>
   <si>
@@ -205,12 +235,12 @@
     <t>TRIPS PRO</t>
   </si>
   <si>
+    <t>6 TRAP</t>
+  </si>
+  <si>
     <t>GIVE @ 2</t>
   </si>
   <si>
-    <t>6 TRAP</t>
-  </si>
-  <si>
     <t>E-Alley</t>
   </si>
   <si>
@@ -220,18 +250,30 @@
     <t>Y TRIPS</t>
   </si>
   <si>
+    <t>RINGO</t>
+  </si>
+  <si>
     <t>Y TRIPS OVER</t>
   </si>
   <si>
+    <t>OLE MISS</t>
+  </si>
+  <si>
     <t>JET</t>
   </si>
   <si>
     <t>Fair Catch</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
     <t>Incomplete</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>PRO</t>
   </si>
   <si>
@@ -244,27 +286,30 @@
     <t>MESH</t>
   </si>
   <si>
+    <t>FAR</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>Y TRIPS WING</t>
+  </si>
+  <si>
+    <t>Complete, Fumble</t>
+  </si>
+  <si>
+    <t>BOOT @ 8</t>
+  </si>
+  <si>
     <t>3 TRAP</t>
   </si>
   <si>
-    <t>FAR</t>
-  </si>
-  <si>
-    <t>Return</t>
-  </si>
-  <si>
-    <t>Y TRIPS WING</t>
-  </si>
-  <si>
-    <t>Complete, Fumble</t>
-  </si>
-  <si>
-    <t>BOOT @ 8</t>
-  </si>
-  <si>
     <t>QB COUNTER</t>
   </si>
   <si>
+    <t>FLEX TEX</t>
+  </si>
+  <si>
     <t>VERTICAL</t>
   </si>
   <si>
@@ -280,18 +325,30 @@
     <t>TACKLE FOLD</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>Rush, TD</t>
   </si>
   <si>
+    <t>DUKE</t>
+  </si>
+  <si>
     <t>TOWARD</t>
   </si>
   <si>
     <t>KO Rec</t>
   </si>
   <si>
+    <t>K TUCK DOT</t>
+  </si>
+  <si>
     <t>Y OFF PRO</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
@@ -301,6 +358,9 @@
     <t>3 SKATE</t>
   </si>
   <si>
+    <t>STR TEX</t>
+  </si>
+  <si>
     <t>WING TRIPS</t>
   </si>
   <si>
@@ -316,12 +376,18 @@
     <t>BOOT @ 9</t>
   </si>
   <si>
+    <t>TANGO</t>
+  </si>
+  <si>
     <t>PRO WING</t>
   </si>
   <si>
     <t>FOLD</t>
   </si>
   <si>
+    <t>WAR</t>
+  </si>
+  <si>
     <t>Sack, Fumble</t>
   </si>
   <si>
@@ -329,13 +395,19 @@
   </si>
   <si>
     <t>FLOOD</t>
+  </si>
+  <si>
+    <t>FLEX</t>
+  </si>
+  <si>
+    <t>SURF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y121"/>
+  <dimension ref="A1:AC121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -413,6 +485,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -422,19 +506,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -457,42 +541,48 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="W3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -504,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -516,39 +606,45 @@
         <v>-20</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L4">
         <v>7</v>
       </c>
       <c r="M4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" t="s">
         <v>38</v>
       </c>
-      <c r="R4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="Q4" t="s">
         <v>39</v>
       </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>34</v>
-      </c>
-      <c r="X4">
+      <c r="W4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -560,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -572,36 +668,45 @@
         <v>-24</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
-      <c r="R5" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" t="s">
-        <v>44</v>
-      </c>
-      <c r="T5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" t="s">
-        <v>37</v>
-      </c>
-      <c r="X5">
+      <c r="P5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
+      <c r="W5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -613,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -625,39 +730,42 @@
         <v>-34</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" t="s">
         <v>38</v>
       </c>
-      <c r="R6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" t="s">
-        <v>46</v>
-      </c>
-      <c r="T6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6">
+      <c r="W6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -669,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -681,19 +789,19 @@
         <v>-34</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J7">
         <v>-3</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -704,22 +812,28 @@
       <c r="O7">
         <v>3</v>
       </c>
-      <c r="R7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" t="s">
-        <v>37</v>
-      </c>
-      <c r="W7">
-        <v>6</v>
-      </c>
-      <c r="X7">
+      <c r="P7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="W7" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -731,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -743,42 +857,51 @@
         <v>-31</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J8">
         <v>-4</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
       <c r="R8" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" t="s">
-        <v>51</v>
-      </c>
-      <c r="T8" t="s">
-        <v>52</v>
-      </c>
-      <c r="U8" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8">
-        <v>6</v>
-      </c>
-      <c r="X8">
+        <v>57</v>
+      </c>
+      <c r="S8">
+        <v>6</v>
+      </c>
+      <c r="W8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -790,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -802,15 +925,15 @@
         <v>-27</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
-      </c>
-      <c r="X9">
+        <v>61</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -822,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -834,36 +957,39 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" t="s">
-        <v>56</v>
-      </c>
-      <c r="S10" t="s">
-        <v>57</v>
-      </c>
-      <c r="U10" t="s">
-        <v>34</v>
-      </c>
-      <c r="X10">
+        <v>37</v>
+      </c>
+      <c r="P10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -875,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -887,36 +1013,39 @@
         <v>42</v>
       </c>
       <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11" t="s">
-        <v>58</v>
-      </c>
-      <c r="U11" t="s">
-        <v>37</v>
-      </c>
-      <c r="X11">
+        <v>44</v>
+      </c>
+      <c r="P11" t="s">
+        <v>63</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -928,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -940,36 +1069,39 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
         <v>37</v>
       </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12">
-        <v>6</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-      <c r="M12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" t="s">
-        <v>59</v>
-      </c>
-      <c r="U12" t="s">
-        <v>37</v>
-      </c>
-      <c r="X12">
+      <c r="P12" t="s">
+        <v>63</v>
+      </c>
+      <c r="W12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -981,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -993,30 +1125,33 @@
         <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L13">
         <v>8</v>
       </c>
-      <c r="S13" t="s">
-        <v>60</v>
-      </c>
-      <c r="U13" t="s">
-        <v>37</v>
-      </c>
-      <c r="X13">
+      <c r="P13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X13" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -1028,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1040,33 +1175,36 @@
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
-      <c r="R14" t="s">
-        <v>34</v>
-      </c>
-      <c r="S14" t="s">
-        <v>61</v>
-      </c>
-      <c r="U14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X14">
+      <c r="P14" t="s">
+        <v>70</v>
+      </c>
+      <c r="W14" t="s">
+        <v>40</v>
+      </c>
+      <c r="X14" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -1078,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1090,18 +1228,18 @@
         <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
-      </c>
-      <c r="X15">
+        <v>49</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1113,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1125,33 +1263,36 @@
         <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L16">
         <v>7</v>
       </c>
-      <c r="R16" t="s">
-        <v>34</v>
-      </c>
-      <c r="S16" t="s">
-        <v>63</v>
-      </c>
-      <c r="U16" t="s">
-        <v>37</v>
-      </c>
-      <c r="X16">
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="W16" t="s">
+        <v>40</v>
+      </c>
+      <c r="X16" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1163,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1175,42 +1316,48 @@
         <v>-26</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J17">
         <v>8</v>
       </c>
       <c r="K17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17" t="s">
-        <v>38</v>
-      </c>
-      <c r="R17" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>39</v>
       </c>
       <c r="S17" t="s">
-        <v>63</v>
-      </c>
-      <c r="T17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U17" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="W17" t="s">
-        <v>65</v>
-      </c>
-      <c r="X17">
+        <v>43</v>
+      </c>
+      <c r="X17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1222,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1234,42 +1381,48 @@
         <v>-34</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
       <c r="K18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
       <c r="M18" t="s">
-        <v>66</v>
-      </c>
-      <c r="R18" t="s">
-        <v>34</v>
-      </c>
-      <c r="S18" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U18" t="s">
-        <v>37</v>
-      </c>
-      <c r="W18">
-        <v>6</v>
-      </c>
-      <c r="X18">
+        <v>76</v>
+      </c>
+      <c r="P18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18">
+        <v>6</v>
+      </c>
+      <c r="W18" t="s">
+        <v>40</v>
+      </c>
+      <c r="X18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1281,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1293,39 +1446,45 @@
         <v>-37</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
-      <c r="R19" t="s">
-        <v>37</v>
-      </c>
-      <c r="S19" t="s">
-        <v>68</v>
-      </c>
-      <c r="T19" t="s">
-        <v>45</v>
-      </c>
-      <c r="U19" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19">
-        <v>3</v>
-      </c>
-      <c r="X19">
+      <c r="P19" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>39</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1337,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1349,42 +1508,48 @@
         <v>-36</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J20">
         <v>9</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20" t="s">
-        <v>29</v>
-      </c>
-      <c r="R20" t="s">
-        <v>34</v>
-      </c>
-      <c r="S20" t="s">
-        <v>69</v>
+        <v>33</v>
+      </c>
+      <c r="P20" t="s">
+        <v>63</v>
+      </c>
+      <c r="S20">
+        <v>3</v>
       </c>
       <c r="T20" t="s">
-        <v>36</v>
-      </c>
-      <c r="U20" t="s">
-        <v>34</v>
-      </c>
-      <c r="W20">
-        <v>3</v>
-      </c>
-      <c r="X20">
+        <v>79</v>
+      </c>
+      <c r="W20" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1396,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1408,45 +1573,51 @@
         <v>-45</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J21">
         <v>-4</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
       <c r="M21" t="s">
-        <v>66</v>
-      </c>
-      <c r="R21" t="s">
-        <v>37</v>
-      </c>
-      <c r="S21" t="s">
-        <v>48</v>
-      </c>
-      <c r="T21" t="s">
-        <v>70</v>
-      </c>
-      <c r="U21" t="s">
-        <v>34</v>
-      </c>
-      <c r="V21" t="s">
-        <v>34</v>
-      </c>
-      <c r="W21">
-        <v>3</v>
-      </c>
-      <c r="X21">
+        <v>76</v>
+      </c>
+      <c r="P21" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>81</v>
+      </c>
+      <c r="S21">
+        <v>3</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1458,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -1470,15 +1641,15 @@
         <v>-41</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>71</v>
-      </c>
-      <c r="X22">
+        <v>83</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1490,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1502,19 +1673,19 @@
         <v>-22</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J23">
         <v>28</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -1525,16 +1696,19 @@
       <c r="O23">
         <v>5</v>
       </c>
-      <c r="R23" t="s">
-        <v>34</v>
-      </c>
-      <c r="S23" t="s">
-        <v>46</v>
-      </c>
-      <c r="U23" t="s">
-        <v>37</v>
-      </c>
-      <c r="X23">
+      <c r="P23" t="s">
+        <v>63</v>
+      </c>
+      <c r="W23" t="s">
+        <v>40</v>
+      </c>
+      <c r="X23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1546,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1558,30 +1732,33 @@
         <v>50</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J24">
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L24">
         <v>7</v>
       </c>
-      <c r="R24" t="s">
-        <v>37</v>
-      </c>
-      <c r="U24" t="s">
-        <v>37</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>84</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1593,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1605,33 +1782,36 @@
         <v>48</v>
       </c>
       <c r="G25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L25">
         <v>7</v>
       </c>
-      <c r="R25" t="s">
-        <v>56</v>
-      </c>
-      <c r="S25" t="s">
-        <v>39</v>
-      </c>
-      <c r="U25" t="s">
-        <v>37</v>
-      </c>
-      <c r="X25">
+      <c r="P25" t="s">
+        <v>63</v>
+      </c>
+      <c r="W25" t="s">
+        <v>64</v>
+      </c>
+      <c r="X25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1643,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1655,27 +1835,30 @@
         <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L26">
         <v>8</v>
       </c>
-      <c r="U26" t="s">
-        <v>34</v>
-      </c>
-      <c r="X26">
+      <c r="P26" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1687,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1699,19 +1882,19 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I27" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -1722,16 +1905,19 @@
       <c r="O27">
         <v>7</v>
       </c>
-      <c r="R27" t="s">
-        <v>37</v>
-      </c>
-      <c r="S27" t="s">
-        <v>48</v>
-      </c>
-      <c r="U27" t="s">
-        <v>34</v>
-      </c>
-      <c r="X27">
+      <c r="P27" t="s">
+        <v>86</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1743,7 +1929,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1755,33 +1941,36 @@
         <v>40</v>
       </c>
       <c r="G28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" t="s">
-        <v>30</v>
-      </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J28">
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
-      <c r="R28" t="s">
-        <v>37</v>
-      </c>
-      <c r="S28" t="s">
-        <v>73</v>
-      </c>
-      <c r="U28" t="s">
-        <v>34</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>70</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1793,7 +1982,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1805,30 +1994,33 @@
         <v>37</v>
       </c>
       <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" t="s">
-        <v>30</v>
-      </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J29">
         <v>-3</v>
       </c>
       <c r="K29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L29">
         <v>6</v>
       </c>
-      <c r="R29" t="s">
-        <v>37</v>
-      </c>
-      <c r="U29" t="s">
-        <v>37</v>
-      </c>
-      <c r="X29">
+      <c r="P29" t="s">
+        <v>29</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1840,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1852,15 +2044,15 @@
         <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s">
-        <v>28</v>
-      </c>
-      <c r="X30">
+        <v>32</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1872,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1884,45 +2076,51 @@
         <v>-20</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J31">
         <v>-3</v>
       </c>
       <c r="K31" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L31">
         <v>7</v>
       </c>
       <c r="M31" t="s">
-        <v>38</v>
-      </c>
-      <c r="R31" t="s">
-        <v>37</v>
-      </c>
-      <c r="S31" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>39</v>
+      </c>
+      <c r="S31">
+        <v>6</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y31" t="s">
         <v>75</v>
       </c>
-      <c r="T31" t="s">
-        <v>64</v>
-      </c>
-      <c r="U31" t="s">
-        <v>37</v>
-      </c>
-      <c r="V31" t="s">
-        <v>37</v>
-      </c>
-      <c r="W31">
-        <v>6</v>
-      </c>
-      <c r="X31">
+      <c r="Z31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB31">
         <v>3</v>
       </c>
     </row>
@@ -1934,7 +2132,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1946,19 +2144,19 @@
         <v>-17</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -1969,22 +2167,28 @@
       <c r="O32">
         <v>6</v>
       </c>
-      <c r="R32" t="s">
-        <v>37</v>
-      </c>
-      <c r="S32" t="s">
-        <v>63</v>
-      </c>
-      <c r="T32" t="s">
-        <v>76</v>
-      </c>
-      <c r="U32" t="s">
-        <v>37</v>
+      <c r="P32" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>39</v>
+      </c>
+      <c r="S32">
+        <v>3</v>
       </c>
       <c r="W32" t="s">
-        <v>77</v>
-      </c>
-      <c r="X32">
+        <v>43</v>
+      </c>
+      <c r="X32" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -1996,7 +2200,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -2008,19 +2212,19 @@
         <v>-17</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I33" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L33">
         <v>6</v>
@@ -2031,19 +2235,31 @@
       <c r="O33">
         <v>5</v>
       </c>
+      <c r="P33" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>39</v>
+      </c>
       <c r="R33" t="s">
-        <v>34</v>
-      </c>
-      <c r="S33" t="s">
-        <v>78</v>
-      </c>
-      <c r="T33" t="s">
-        <v>76</v>
-      </c>
-      <c r="U33" t="s">
-        <v>37</v>
-      </c>
-      <c r="X33">
+        <v>57</v>
+      </c>
+      <c r="S33">
+        <v>3</v>
+      </c>
+      <c r="W33" t="s">
+        <v>40</v>
+      </c>
+      <c r="X33" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -2055,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -2067,18 +2283,18 @@
         <v>-17</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34">
-        <v>6</v>
-      </c>
-      <c r="X34">
+        <v>92</v>
+      </c>
+      <c r="V34">
+        <v>6</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -2090,7 +2306,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2102,19 +2318,19 @@
         <v>-48</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I35" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J35">
         <v>11</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -2125,16 +2341,19 @@
       <c r="O35">
         <v>2</v>
       </c>
-      <c r="R35" t="s">
-        <v>34</v>
-      </c>
-      <c r="S35" t="s">
-        <v>46</v>
-      </c>
-      <c r="U35" t="s">
-        <v>34</v>
-      </c>
-      <c r="X35">
+      <c r="P35" t="s">
+        <v>63</v>
+      </c>
+      <c r="W35" t="s">
+        <v>40</v>
+      </c>
+      <c r="X35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -2146,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2158,33 +2377,36 @@
         <v>41</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
-      <c r="R36" t="s">
-        <v>37</v>
-      </c>
-      <c r="S36" t="s">
-        <v>48</v>
-      </c>
-      <c r="U36" t="s">
-        <v>34</v>
-      </c>
-      <c r="X36">
+      <c r="P36" t="s">
+        <v>63</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -2196,7 +2418,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2208,33 +2430,36 @@
         <v>37</v>
       </c>
       <c r="G37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" t="s">
-        <v>30</v>
-      </c>
       <c r="I37" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J37">
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
-      <c r="R37" t="s">
-        <v>37</v>
-      </c>
-      <c r="S37" t="s">
-        <v>80</v>
-      </c>
-      <c r="U37" t="s">
-        <v>34</v>
-      </c>
-      <c r="X37">
+      <c r="P37" t="s">
+        <v>63</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -2246,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -2258,19 +2483,19 @@
         <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I38" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -2281,16 +2506,19 @@
       <c r="O38">
         <v>2</v>
       </c>
-      <c r="R38" t="s">
-        <v>37</v>
-      </c>
-      <c r="S38" t="s">
-        <v>63</v>
-      </c>
-      <c r="U38" t="s">
-        <v>37</v>
-      </c>
-      <c r="X38">
+      <c r="P38" t="s">
+        <v>86</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2302,7 +2530,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2314,36 +2542,45 @@
         <v>-22</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I39" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J39">
         <v>2</v>
       </c>
       <c r="K39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L39">
         <v>6</v>
       </c>
-      <c r="R39" t="s">
-        <v>34</v>
-      </c>
-      <c r="S39" t="s">
-        <v>78</v>
-      </c>
-      <c r="T39" t="s">
-        <v>82</v>
-      </c>
-      <c r="U39" t="s">
-        <v>34</v>
-      </c>
-      <c r="X39">
+      <c r="P39" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>39</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="W39" t="s">
+        <v>40</v>
+      </c>
+      <c r="X39" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB39">
         <v>4</v>
       </c>
     </row>
@@ -2355,7 +2592,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2367,42 +2604,48 @@
         <v>-24</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J40">
         <v>-2</v>
       </c>
       <c r="K40" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L40">
         <v>8</v>
       </c>
       <c r="M40" t="s">
+        <v>44</v>
+      </c>
+      <c r="P40" t="s">
         <v>38</v>
       </c>
-      <c r="R40" t="s">
-        <v>34</v>
+      <c r="Q40" t="s">
+        <v>39</v>
       </c>
       <c r="S40" t="s">
-        <v>46</v>
-      </c>
-      <c r="T40" t="s">
-        <v>83</v>
-      </c>
-      <c r="U40" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="W40" t="s">
-        <v>77</v>
-      </c>
-      <c r="X40">
+        <v>40</v>
+      </c>
+      <c r="X40" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB40">
         <v>4</v>
       </c>
     </row>
@@ -2414,7 +2657,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2426,19 +2669,19 @@
         <v>-22</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I41" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -2449,22 +2692,31 @@
       <c r="O41">
         <v>5</v>
       </c>
+      <c r="P41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>39</v>
+      </c>
       <c r="R41" t="s">
-        <v>34</v>
-      </c>
-      <c r="S41" t="s">
-        <v>44</v>
-      </c>
-      <c r="T41" t="s">
-        <v>84</v>
-      </c>
-      <c r="U41" t="s">
-        <v>37</v>
-      </c>
-      <c r="W41">
-        <v>6</v>
-      </c>
-      <c r="X41">
+        <v>98</v>
+      </c>
+      <c r="S41">
+        <v>6</v>
+      </c>
+      <c r="W41" t="s">
+        <v>40</v>
+      </c>
+      <c r="X41" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB41">
         <v>4</v>
       </c>
     </row>
@@ -2476,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2488,15 +2740,15 @@
         <v>-22</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
-      </c>
-      <c r="X42">
+        <v>83</v>
+      </c>
+      <c r="AB42">
         <v>4</v>
       </c>
     </row>
@@ -2508,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2520,19 +2772,19 @@
         <v>-41</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I43" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J43">
         <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L43">
         <v>6</v>
@@ -2543,16 +2795,19 @@
       <c r="O43">
         <v>3</v>
       </c>
-      <c r="R43" t="s">
-        <v>37</v>
-      </c>
-      <c r="S43" t="s">
-        <v>46</v>
-      </c>
-      <c r="U43" t="s">
-        <v>37</v>
-      </c>
-      <c r="X43">
+      <c r="P43" t="s">
+        <v>63</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB43">
         <v>4</v>
       </c>
     </row>
@@ -2564,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -2576,33 +2831,36 @@
         <v>-47</v>
       </c>
       <c r="G44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L44">
         <v>7</v>
       </c>
-      <c r="R44" t="s">
-        <v>56</v>
-      </c>
-      <c r="S44" t="s">
-        <v>39</v>
-      </c>
-      <c r="U44" t="s">
-        <v>34</v>
-      </c>
-      <c r="X44">
+      <c r="P44" t="s">
+        <v>63</v>
+      </c>
+      <c r="W44" t="s">
+        <v>64</v>
+      </c>
+      <c r="X44" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB44">
         <v>4</v>
       </c>
     </row>
@@ -2614,7 +2872,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -2626,19 +2884,19 @@
         <v>-47</v>
       </c>
       <c r="G45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I45" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J45">
         <v>53</v>
       </c>
       <c r="K45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L45">
         <v>6</v>
@@ -2649,13 +2907,16 @@
       <c r="O45">
         <v>1</v>
       </c>
-      <c r="R45" t="s">
-        <v>34</v>
-      </c>
-      <c r="U45" t="s">
-        <v>34</v>
-      </c>
-      <c r="X45">
+      <c r="P45" t="s">
+        <v>38</v>
+      </c>
+      <c r="W45" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -2667,7 +2928,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2676,15 +2937,15 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
-      </c>
-      <c r="X46">
+        <v>102</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2696,19 +2957,19 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F47">
         <v>-40</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I47" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -2719,7 +2980,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2731,42 +2992,48 @@
         <v>-20</v>
       </c>
       <c r="G48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" t="s">
-        <v>30</v>
-      </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J48">
         <v>-2</v>
       </c>
       <c r="K48" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L48">
         <v>6</v>
       </c>
       <c r="M48" t="s">
-        <v>38</v>
-      </c>
-      <c r="R48" t="s">
-        <v>34</v>
-      </c>
-      <c r="S48" t="s">
-        <v>78</v>
-      </c>
-      <c r="T48" t="s">
-        <v>88</v>
-      </c>
-      <c r="U48" t="s">
-        <v>34</v>
-      </c>
-      <c r="W48">
-        <v>3</v>
-      </c>
-      <c r="X48">
+        <v>44</v>
+      </c>
+      <c r="P48" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>39</v>
+      </c>
+      <c r="S48">
+        <v>3</v>
+      </c>
+      <c r="W48" t="s">
+        <v>40</v>
+      </c>
+      <c r="X48" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2778,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2790,19 +3057,19 @@
         <v>-18</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I49" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -2813,22 +3080,28 @@
       <c r="O49">
         <v>1</v>
       </c>
-      <c r="R49" t="s">
-        <v>37</v>
-      </c>
-      <c r="S49" t="s">
+      <c r="P49" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q49" t="s">
         <v>39</v>
       </c>
-      <c r="T49" t="s">
-        <v>84</v>
-      </c>
-      <c r="U49" t="s">
-        <v>34</v>
-      </c>
-      <c r="W49">
-        <v>3</v>
-      </c>
-      <c r="X49">
+      <c r="S49">
+        <v>3</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2840,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2852,19 +3125,19 @@
         <v>-18</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J50">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L50">
         <v>6</v>
@@ -2875,22 +3148,31 @@
       <c r="O50">
         <v>2</v>
       </c>
+      <c r="P50" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>39</v>
+      </c>
       <c r="R50" t="s">
-        <v>37</v>
-      </c>
-      <c r="S50" t="s">
-        <v>44</v>
-      </c>
-      <c r="T50" t="s">
-        <v>45</v>
-      </c>
-      <c r="U50" t="s">
-        <v>37</v>
-      </c>
-      <c r="W50">
-        <v>6</v>
-      </c>
-      <c r="X50">
+        <v>98</v>
+      </c>
+      <c r="S50">
+        <v>6</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2902,7 +3184,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2914,15 +3196,15 @@
         <v>-25</v>
       </c>
       <c r="G51" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H51" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I51" t="s">
-        <v>71</v>
-      </c>
-      <c r="X51">
+        <v>83</v>
+      </c>
+      <c r="AB51">
         <v>4</v>
       </c>
     </row>
@@ -2934,7 +3216,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2946,30 +3228,33 @@
         <v>-40</v>
       </c>
       <c r="G52" t="s">
+        <v>40</v>
+      </c>
+      <c r="H52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" t="s">
-        <v>30</v>
-      </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J52">
         <v>3</v>
       </c>
       <c r="K52" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L52">
         <v>6</v>
       </c>
-      <c r="R52" t="s">
-        <v>56</v>
-      </c>
-      <c r="U52" t="s">
-        <v>34</v>
-      </c>
-      <c r="X52">
+      <c r="P52" t="s">
+        <v>63</v>
+      </c>
+      <c r="W52" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB52">
         <v>5</v>
       </c>
     </row>
@@ -2981,7 +3266,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -2993,33 +3278,36 @@
         <v>-43</v>
       </c>
       <c r="G53" t="s">
+        <v>40</v>
+      </c>
+      <c r="H53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" t="s">
-        <v>30</v>
-      </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J53">
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L53">
         <v>7</v>
       </c>
-      <c r="R53" t="s">
-        <v>56</v>
-      </c>
-      <c r="S53" t="s">
-        <v>39</v>
-      </c>
-      <c r="U53" t="s">
-        <v>34</v>
-      </c>
-      <c r="X53">
+      <c r="P53" t="s">
+        <v>63</v>
+      </c>
+      <c r="W53" t="s">
+        <v>64</v>
+      </c>
+      <c r="X53" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB53">
         <v>5</v>
       </c>
     </row>
@@ -3031,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -3043,19 +3331,19 @@
         <v>-45</v>
       </c>
       <c r="G54" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I54" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J54">
         <v>11</v>
       </c>
       <c r="K54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L54">
         <v>6</v>
@@ -3066,13 +3354,16 @@
       <c r="O54">
         <v>6</v>
       </c>
-      <c r="R54" t="s">
-        <v>37</v>
-      </c>
-      <c r="U54" t="s">
-        <v>37</v>
-      </c>
-      <c r="X54">
+      <c r="P54" t="s">
+        <v>29</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB54">
         <v>5</v>
       </c>
     </row>
@@ -3084,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3096,19 +3387,19 @@
         <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I55" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J55">
         <v>41</v>
       </c>
       <c r="K55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L55">
         <v>6</v>
@@ -3119,16 +3410,19 @@
       <c r="O55">
         <v>7</v>
       </c>
-      <c r="R55" t="s">
-        <v>56</v>
-      </c>
-      <c r="S55" t="s">
-        <v>39</v>
-      </c>
-      <c r="U55" t="s">
-        <v>34</v>
-      </c>
-      <c r="X55">
+      <c r="P55" t="s">
+        <v>104</v>
+      </c>
+      <c r="W55" t="s">
+        <v>64</v>
+      </c>
+      <c r="X55" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55">
         <v>5</v>
       </c>
     </row>
@@ -3140,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3152,33 +3446,36 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
+        <v>40</v>
+      </c>
+      <c r="H56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" t="s">
-        <v>30</v>
-      </c>
       <c r="I56" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J56">
         <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L56">
         <v>9</v>
       </c>
-      <c r="R56" t="s">
-        <v>37</v>
-      </c>
-      <c r="S56" t="s">
-        <v>46</v>
-      </c>
-      <c r="U56" t="s">
-        <v>37</v>
-      </c>
-      <c r="X56">
+      <c r="P56" t="s">
+        <v>63</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB56">
         <v>5</v>
       </c>
     </row>
@@ -3190,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3199,15 +3496,15 @@
         <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I57" t="s">
-        <v>87</v>
-      </c>
-      <c r="X57">
+        <v>102</v>
+      </c>
+      <c r="AB57">
         <v>5</v>
       </c>
     </row>
@@ -3219,7 +3516,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3228,18 +3525,18 @@
         <v>-40</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q58">
+        <v>92</v>
+      </c>
+      <c r="V58">
         <v>22</v>
       </c>
-      <c r="X58">
+      <c r="AB58">
         <v>6</v>
       </c>
     </row>
@@ -3251,7 +3548,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3263,42 +3560,48 @@
         <v>-29</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J59">
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L59">
         <v>5</v>
       </c>
       <c r="M59" t="s">
-        <v>33</v>
-      </c>
-      <c r="R59" t="s">
         <v>37</v>
       </c>
-      <c r="S59" t="s">
-        <v>44</v>
-      </c>
-      <c r="T59" t="s">
-        <v>90</v>
-      </c>
-      <c r="U59" t="s">
-        <v>37</v>
-      </c>
-      <c r="W59">
-        <v>6</v>
-      </c>
-      <c r="X59">
+      <c r="P59" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>106</v>
+      </c>
+      <c r="S59">
+        <v>6</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -3310,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3322,15 +3625,15 @@
         <v>-40</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="I60" t="s">
-        <v>28</v>
-      </c>
-      <c r="X60">
+        <v>32</v>
+      </c>
+      <c r="AB60">
         <v>5</v>
       </c>
     </row>
@@ -3342,7 +3645,7 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3354,33 +3657,36 @@
         <v>-20</v>
       </c>
       <c r="G61" t="s">
+        <v>40</v>
+      </c>
+      <c r="H61" t="s">
         <v>34</v>
       </c>
-      <c r="H61" t="s">
-        <v>30</v>
-      </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J61">
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L61">
         <v>8</v>
       </c>
-      <c r="R61" t="s">
-        <v>37</v>
-      </c>
-      <c r="S61" t="s">
-        <v>92</v>
-      </c>
-      <c r="U61" t="s">
-        <v>34</v>
-      </c>
-      <c r="X61">
+      <c r="P61" t="s">
+        <v>109</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3392,7 +3698,7 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3404,33 +3710,36 @@
         <v>-29</v>
       </c>
       <c r="G62" t="s">
+        <v>40</v>
+      </c>
+      <c r="H62" t="s">
         <v>34</v>
       </c>
-      <c r="H62" t="s">
-        <v>30</v>
-      </c>
       <c r="I62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L62">
         <v>8</v>
       </c>
-      <c r="R62" t="s">
-        <v>37</v>
-      </c>
-      <c r="S62" t="s">
-        <v>92</v>
-      </c>
-      <c r="U62" t="s">
-        <v>34</v>
-      </c>
-      <c r="X62">
+      <c r="P62" t="s">
+        <v>109</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3442,7 +3751,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -3454,33 +3763,36 @@
         <v>-29</v>
       </c>
       <c r="G63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H63" t="s">
         <v>34</v>
       </c>
-      <c r="H63" t="s">
-        <v>30</v>
-      </c>
       <c r="I63" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J63">
         <v>2</v>
       </c>
       <c r="K63" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L63">
         <v>7</v>
       </c>
-      <c r="R63" t="s">
-        <v>56</v>
-      </c>
-      <c r="S63" t="s">
-        <v>35</v>
-      </c>
-      <c r="U63" t="s">
-        <v>34</v>
-      </c>
-      <c r="X63">
+      <c r="P63" t="s">
+        <v>111</v>
+      </c>
+      <c r="W63" t="s">
+        <v>64</v>
+      </c>
+      <c r="X63" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3492,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3504,33 +3816,36 @@
         <v>-31</v>
       </c>
       <c r="G64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H64" t="s">
         <v>34</v>
       </c>
-      <c r="H64" t="s">
-        <v>30</v>
-      </c>
       <c r="I64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J64">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L64">
         <v>7</v>
       </c>
-      <c r="R64" t="s">
-        <v>37</v>
-      </c>
-      <c r="S64" t="s">
-        <v>80</v>
-      </c>
-      <c r="U64" t="s">
-        <v>37</v>
-      </c>
-      <c r="X64">
+      <c r="P64" t="s">
+        <v>63</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB64">
         <v>4</v>
       </c>
     </row>
@@ -3542,7 +3857,7 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3554,33 +3869,36 @@
         <v>-35</v>
       </c>
       <c r="G65" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J65">
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L65">
         <v>7</v>
       </c>
-      <c r="R65" t="s">
-        <v>56</v>
-      </c>
-      <c r="S65" t="s">
-        <v>39</v>
-      </c>
-      <c r="U65" t="s">
-        <v>37</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>63</v>
+      </c>
+      <c r="W65" t="s">
+        <v>64</v>
+      </c>
+      <c r="X65" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB65">
         <v>4</v>
       </c>
     </row>
@@ -3592,7 +3910,7 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -3604,27 +3922,30 @@
         <v>-38</v>
       </c>
       <c r="G66" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J66">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L66">
         <v>7</v>
       </c>
-      <c r="U66" t="s">
-        <v>34</v>
-      </c>
-      <c r="X66">
+      <c r="P66" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB66">
         <v>4</v>
       </c>
     </row>
@@ -3636,7 +3957,7 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -3648,18 +3969,18 @@
         <v>-39</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J67">
         <v>-5</v>
       </c>
-      <c r="X67">
+      <c r="AB67">
         <v>4</v>
       </c>
     </row>
@@ -3671,7 +3992,7 @@
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3683,15 +4004,15 @@
         <v>-34</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H68" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
-      </c>
-      <c r="X68">
+        <v>113</v>
+      </c>
+      <c r="AB68">
         <v>4</v>
       </c>
     </row>
@@ -3703,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3715,42 +4036,48 @@
         <v>-26</v>
       </c>
       <c r="G69" t="s">
+        <v>43</v>
+      </c>
+      <c r="H69" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69">
+        <v>7</v>
+      </c>
+      <c r="M69" t="s">
         <v>37</v>
       </c>
-      <c r="H69" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" t="s">
-        <v>31</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69" t="s">
-        <v>32</v>
-      </c>
-      <c r="L69">
-        <v>7</v>
-      </c>
-      <c r="M69" t="s">
-        <v>33</v>
-      </c>
-      <c r="R69" t="s">
-        <v>34</v>
+      <c r="P69" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>39</v>
       </c>
       <c r="S69" t="s">
-        <v>63</v>
-      </c>
-      <c r="T69" t="s">
-        <v>64</v>
-      </c>
-      <c r="U69" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="W69" t="s">
-        <v>95</v>
-      </c>
-      <c r="X69">
+        <v>40</v>
+      </c>
+      <c r="X69" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB69">
         <v>6</v>
       </c>
     </row>
@@ -3762,7 +4089,7 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3774,42 +4101,48 @@
         <v>-27</v>
       </c>
       <c r="G70" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J70">
         <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L70">
         <v>6</v>
       </c>
       <c r="M70" t="s">
-        <v>66</v>
-      </c>
-      <c r="R70" t="s">
-        <v>34</v>
+        <v>76</v>
+      </c>
+      <c r="P70" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>39</v>
       </c>
       <c r="S70" t="s">
-        <v>44</v>
-      </c>
-      <c r="T70" t="s">
-        <v>67</v>
-      </c>
-      <c r="U70" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="W70" t="s">
-        <v>95</v>
-      </c>
-      <c r="X70">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB70">
         <v>6</v>
       </c>
     </row>
@@ -3821,7 +4154,7 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3833,42 +4166,48 @@
         <v>-40</v>
       </c>
       <c r="G71" t="s">
+        <v>40</v>
+      </c>
+      <c r="H71" t="s">
         <v>34</v>
       </c>
-      <c r="H71" t="s">
-        <v>30</v>
-      </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L71">
         <v>7</v>
       </c>
       <c r="M71" t="s">
-        <v>33</v>
-      </c>
-      <c r="R71" t="s">
-        <v>34</v>
-      </c>
-      <c r="S71" t="s">
-        <v>96</v>
-      </c>
-      <c r="T71" t="s">
-        <v>36</v>
-      </c>
-      <c r="U71" t="s">
-        <v>34</v>
-      </c>
-      <c r="W71">
-        <v>3</v>
-      </c>
-      <c r="X71">
+        <v>37</v>
+      </c>
+      <c r="P71" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>115</v>
+      </c>
+      <c r="S71">
+        <v>3</v>
+      </c>
+      <c r="W71" t="s">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB71">
         <v>6</v>
       </c>
     </row>
@@ -3880,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3892,42 +4231,48 @@
         <v>-40</v>
       </c>
       <c r="G72" t="s">
+        <v>40</v>
+      </c>
+      <c r="H72" t="s">
         <v>34</v>
       </c>
-      <c r="H72" t="s">
-        <v>30</v>
-      </c>
       <c r="I72" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J72">
         <v>-1</v>
       </c>
       <c r="K72" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L72">
         <v>7</v>
       </c>
       <c r="M72" t="s">
-        <v>66</v>
-      </c>
-      <c r="R72" t="s">
-        <v>37</v>
-      </c>
-      <c r="S72" t="s">
-        <v>48</v>
-      </c>
-      <c r="T72" t="s">
-        <v>67</v>
-      </c>
-      <c r="U72" t="s">
-        <v>37</v>
-      </c>
-      <c r="W72">
-        <v>3</v>
-      </c>
-      <c r="X72">
+        <v>76</v>
+      </c>
+      <c r="P72" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>39</v>
+      </c>
+      <c r="S72">
+        <v>3</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB72">
         <v>6</v>
       </c>
     </row>
@@ -3939,7 +4284,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -3951,39 +4296,48 @@
         <v>-39</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I73" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J73">
         <v>-9</v>
       </c>
       <c r="K73" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L73">
         <v>7</v>
       </c>
+      <c r="P73" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>39</v>
+      </c>
       <c r="R73" t="s">
-        <v>34</v>
-      </c>
-      <c r="S73" t="s">
-        <v>63</v>
-      </c>
-      <c r="T73" t="s">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s">
-        <v>34</v>
-      </c>
-      <c r="W73">
-        <v>6</v>
-      </c>
-      <c r="X73">
+        <v>98</v>
+      </c>
+      <c r="S73">
+        <v>6</v>
+      </c>
+      <c r="W73" t="s">
+        <v>40</v>
+      </c>
+      <c r="X73" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB73">
         <v>6</v>
       </c>
     </row>
@@ -3995,7 +4349,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -4007,15 +4361,15 @@
         <v>-30</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I74" t="s">
-        <v>71</v>
-      </c>
-      <c r="X74">
+        <v>83</v>
+      </c>
+      <c r="AB74">
         <v>6</v>
       </c>
     </row>
@@ -4027,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -4039,36 +4393,39 @@
         <v>-34</v>
       </c>
       <c r="G75" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J75">
         <v>6</v>
       </c>
       <c r="K75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
-      <c r="Q75">
+      <c r="P75" t="s">
+        <v>63</v>
+      </c>
+      <c r="V75">
         <v>0</v>
       </c>
-      <c r="R75" t="s">
-        <v>56</v>
-      </c>
-      <c r="S75" t="s">
-        <v>39</v>
-      </c>
-      <c r="U75" t="s">
-        <v>34</v>
-      </c>
-      <c r="X75">
+      <c r="W75" t="s">
+        <v>64</v>
+      </c>
+      <c r="X75" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -4080,7 +4437,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4092,33 +4449,36 @@
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L76">
         <v>7</v>
       </c>
-      <c r="R76" t="s">
-        <v>56</v>
-      </c>
-      <c r="S76" t="s">
-        <v>39</v>
-      </c>
-      <c r="U76" t="s">
-        <v>37</v>
-      </c>
-      <c r="X76">
+      <c r="P76" t="s">
+        <v>63</v>
+      </c>
+      <c r="W76" t="s">
+        <v>64</v>
+      </c>
+      <c r="X76" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -4130,7 +4490,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -4142,19 +4502,19 @@
         <v>-40</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I77" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J77">
         <v>30</v>
       </c>
       <c r="K77" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L77">
         <v>6</v>
@@ -4165,16 +4525,19 @@
       <c r="O77">
         <v>9</v>
       </c>
-      <c r="R77" t="s">
-        <v>56</v>
-      </c>
-      <c r="S77" t="s">
-        <v>39</v>
-      </c>
-      <c r="U77" t="s">
-        <v>37</v>
-      </c>
-      <c r="X77">
+      <c r="P77" t="s">
+        <v>63</v>
+      </c>
+      <c r="W77" t="s">
+        <v>64</v>
+      </c>
+      <c r="X77" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -4186,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4198,33 +4561,36 @@
         <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J78">
         <v>7</v>
       </c>
       <c r="K78" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L78">
         <v>7</v>
       </c>
-      <c r="R78" t="s">
-        <v>34</v>
-      </c>
-      <c r="S78" t="s">
-        <v>80</v>
-      </c>
-      <c r="U78" t="s">
-        <v>34</v>
-      </c>
-      <c r="X78">
+      <c r="P78" t="s">
+        <v>63</v>
+      </c>
+      <c r="W78" t="s">
+        <v>40</v>
+      </c>
+      <c r="X78" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -4236,7 +4602,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4248,33 +4614,36 @@
         <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J79">
         <v>4</v>
       </c>
       <c r="K79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L79">
         <v>7</v>
       </c>
-      <c r="R79" t="s">
-        <v>56</v>
-      </c>
-      <c r="S79" t="s">
-        <v>39</v>
-      </c>
-      <c r="U79" t="s">
-        <v>34</v>
-      </c>
-      <c r="X79">
+      <c r="P79" t="s">
+        <v>63</v>
+      </c>
+      <c r="W79" t="s">
+        <v>64</v>
+      </c>
+      <c r="X79" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -4286,7 +4655,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4298,33 +4667,36 @@
         <v>19</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J80">
         <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L80">
         <v>7</v>
       </c>
-      <c r="R80" t="s">
-        <v>37</v>
-      </c>
-      <c r="S80" t="s">
-        <v>80</v>
-      </c>
-      <c r="U80" t="s">
-        <v>37</v>
-      </c>
-      <c r="X80">
+      <c r="P80" t="s">
+        <v>63</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -4336,7 +4708,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -4348,33 +4720,36 @@
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H81" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J81">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L81">
         <v>7</v>
       </c>
-      <c r="R81" t="s">
-        <v>56</v>
-      </c>
-      <c r="S81" t="s">
-        <v>39</v>
-      </c>
-      <c r="U81" t="s">
-        <v>37</v>
-      </c>
-      <c r="X81">
+      <c r="P81" t="s">
+        <v>63</v>
+      </c>
+      <c r="W81" t="s">
+        <v>64</v>
+      </c>
+      <c r="X81" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -4386,7 +4761,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -4398,33 +4773,36 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H82" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I82" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J82">
         <v>9</v>
       </c>
       <c r="K82" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L82">
         <v>7</v>
       </c>
-      <c r="R82" t="s">
-        <v>34</v>
-      </c>
-      <c r="S82" t="s">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s">
-        <v>34</v>
-      </c>
-      <c r="X82">
+      <c r="P82" t="s">
+        <v>63</v>
+      </c>
+      <c r="W82" t="s">
+        <v>40</v>
+      </c>
+      <c r="X82" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82">
         <v>5</v>
       </c>
     </row>
@@ -4436,7 +4814,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4448,33 +4826,36 @@
         <v>4</v>
       </c>
       <c r="G83" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" t="s">
         <v>34</v>
       </c>
-      <c r="H83" t="s">
-        <v>30</v>
-      </c>
       <c r="I83" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J83">
         <v>3</v>
       </c>
       <c r="K83" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L83">
         <v>8</v>
       </c>
-      <c r="R83" t="s">
-        <v>37</v>
-      </c>
-      <c r="S83" t="s">
-        <v>80</v>
-      </c>
-      <c r="U83" t="s">
-        <v>37</v>
-      </c>
-      <c r="X83">
+      <c r="P83" t="s">
+        <v>63</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB83">
         <v>5</v>
       </c>
     </row>
@@ -4486,7 +4867,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4498,33 +4879,36 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I84" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J84">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L84">
         <v>9</v>
       </c>
-      <c r="R84" t="s">
-        <v>37</v>
-      </c>
-      <c r="S84" t="s">
-        <v>97</v>
-      </c>
-      <c r="U84" t="s">
-        <v>37</v>
-      </c>
-      <c r="X84">
+      <c r="P84" t="s">
+        <v>111</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB84">
         <v>5</v>
       </c>
     </row>
@@ -4536,7 +4920,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -4545,15 +4929,15 @@
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H85" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I85" t="s">
-        <v>87</v>
-      </c>
-      <c r="X85">
+        <v>102</v>
+      </c>
+      <c r="AB85">
         <v>5</v>
       </c>
     </row>
@@ -4565,7 +4949,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4574,18 +4958,18 @@
         <v>-40</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q86">
+        <v>92</v>
+      </c>
+      <c r="V86">
         <v>17</v>
       </c>
-      <c r="X86">
+      <c r="AB86">
         <v>6</v>
       </c>
     </row>
@@ -4597,7 +4981,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4609,19 +4993,19 @@
         <v>-21</v>
       </c>
       <c r="G87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H87" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I87" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J87">
         <v>14</v>
       </c>
       <c r="K87" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L87">
         <v>7</v>
@@ -4632,22 +5016,31 @@
       <c r="O87">
         <v>5</v>
       </c>
-      <c r="R87" t="s">
-        <v>37</v>
-      </c>
-      <c r="S87" t="s">
-        <v>48</v>
-      </c>
-      <c r="T87" t="s">
-        <v>82</v>
-      </c>
-      <c r="U87" t="s">
-        <v>37</v>
-      </c>
-      <c r="V87" t="s">
-        <v>34</v>
-      </c>
-      <c r="X87">
+      <c r="P87" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>39</v>
+      </c>
+      <c r="S87">
+        <v>3</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB87">
         <v>5</v>
       </c>
     </row>
@@ -4659,7 +5052,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4671,39 +5064,45 @@
         <v>-35</v>
       </c>
       <c r="G88" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J88">
         <v>3</v>
       </c>
       <c r="K88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L88">
         <v>7</v>
       </c>
       <c r="M88" t="s">
-        <v>38</v>
-      </c>
-      <c r="R88" t="s">
-        <v>34</v>
-      </c>
-      <c r="S88" t="s">
-        <v>46</v>
-      </c>
-      <c r="T88" t="s">
-        <v>36</v>
-      </c>
-      <c r="U88" t="s">
-        <v>34</v>
-      </c>
-      <c r="X88">
+        <v>44</v>
+      </c>
+      <c r="P88" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>39</v>
+      </c>
+      <c r="W88" t="s">
+        <v>40</v>
+      </c>
+      <c r="X88" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB88">
         <v>5</v>
       </c>
     </row>
@@ -4715,7 +5114,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4735,7 +5134,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4747,42 +5146,48 @@
         <v>-38</v>
       </c>
       <c r="G90" t="s">
+        <v>40</v>
+      </c>
+      <c r="H90" t="s">
         <v>34</v>
       </c>
-      <c r="H90" t="s">
-        <v>30</v>
-      </c>
       <c r="I90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L90">
         <v>6</v>
       </c>
       <c r="M90" t="s">
+        <v>44</v>
+      </c>
+      <c r="P90" t="s">
         <v>38</v>
       </c>
-      <c r="R90" t="s">
-        <v>37</v>
+      <c r="Q90" t="s">
+        <v>39</v>
       </c>
       <c r="S90" t="s">
-        <v>63</v>
-      </c>
-      <c r="T90" t="s">
-        <v>64</v>
-      </c>
-      <c r="U90" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="W90" t="s">
-        <v>65</v>
-      </c>
-      <c r="X90">
+        <v>43</v>
+      </c>
+      <c r="X90" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB90">
         <v>5</v>
       </c>
     </row>
@@ -4794,7 +5199,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -4806,19 +5211,19 @@
         <v>-38</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H91" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I91" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L91">
         <v>6</v>
@@ -4829,22 +5234,28 @@
       <c r="O91">
         <v>4</v>
       </c>
-      <c r="R91" t="s">
-        <v>37</v>
-      </c>
-      <c r="S91" t="s">
-        <v>44</v>
-      </c>
-      <c r="T91" t="s">
-        <v>45</v>
-      </c>
-      <c r="U91" t="s">
-        <v>34</v>
-      </c>
-      <c r="W91">
-        <v>6</v>
-      </c>
-      <c r="X91">
+      <c r="P91" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>39</v>
+      </c>
+      <c r="S91">
+        <v>6</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB91">
         <v>5</v>
       </c>
     </row>
@@ -4856,7 +5267,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D92">
         <v>4</v>
@@ -4868,15 +5279,15 @@
         <v>-38</v>
       </c>
       <c r="G92" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H92" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I92" t="s">
-        <v>71</v>
-      </c>
-      <c r="X92">
+        <v>83</v>
+      </c>
+      <c r="AB92">
         <v>5</v>
       </c>
     </row>
@@ -4888,7 +5299,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4900,36 +5311,39 @@
         <v>-32</v>
       </c>
       <c r="G93" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J93">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L93">
         <v>7</v>
       </c>
-      <c r="Q93">
+      <c r="P93" t="s">
+        <v>63</v>
+      </c>
+      <c r="V93">
         <v>0</v>
       </c>
-      <c r="R93" t="s">
-        <v>37</v>
-      </c>
-      <c r="S93" t="s">
-        <v>46</v>
-      </c>
-      <c r="U93" t="s">
-        <v>34</v>
-      </c>
-      <c r="X93">
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB93">
         <v>7</v>
       </c>
     </row>
@@ -4941,7 +5355,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4953,33 +5367,36 @@
         <v>-33</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J94">
         <v>3</v>
       </c>
       <c r="K94" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L94">
         <v>7</v>
       </c>
-      <c r="R94" t="s">
-        <v>37</v>
-      </c>
-      <c r="S94" t="s">
-        <v>46</v>
-      </c>
-      <c r="U94" t="s">
-        <v>34</v>
-      </c>
-      <c r="X94">
+      <c r="P94" t="s">
+        <v>63</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94">
         <v>7</v>
       </c>
     </row>
@@ -4991,7 +5408,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -5003,19 +5420,19 @@
         <v>-36</v>
       </c>
       <c r="G95" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H95" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I95" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J95">
         <v>8</v>
       </c>
       <c r="K95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L95">
         <v>7</v>
@@ -5026,16 +5443,19 @@
       <c r="O95">
         <v>3</v>
       </c>
-      <c r="R95" t="s">
-        <v>37</v>
-      </c>
-      <c r="S95" t="s">
-        <v>99</v>
-      </c>
-      <c r="U95" t="s">
-        <v>37</v>
-      </c>
-      <c r="X95">
+      <c r="P95" t="s">
+        <v>38</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB95">
         <v>7</v>
       </c>
     </row>
@@ -5047,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5059,33 +5479,36 @@
         <v>-44</v>
       </c>
       <c r="G96" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J96">
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L96">
         <v>7</v>
       </c>
-      <c r="R96" t="s">
-        <v>56</v>
-      </c>
-      <c r="S96" t="s">
-        <v>39</v>
-      </c>
-      <c r="U96" t="s">
-        <v>37</v>
-      </c>
-      <c r="X96">
+      <c r="P96" t="s">
+        <v>63</v>
+      </c>
+      <c r="W96" t="s">
+        <v>64</v>
+      </c>
+      <c r="X96" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -5097,7 +5520,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5109,33 +5532,36 @@
         <v>-46</v>
       </c>
       <c r="G97" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J97">
         <v>-2</v>
       </c>
       <c r="K97" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L97">
         <v>7</v>
       </c>
-      <c r="R97" t="s">
-        <v>34</v>
-      </c>
-      <c r="S97" t="s">
-        <v>96</v>
-      </c>
-      <c r="U97" t="s">
-        <v>37</v>
-      </c>
-      <c r="X97">
+      <c r="P97" t="s">
+        <v>63</v>
+      </c>
+      <c r="W97" t="s">
+        <v>40</v>
+      </c>
+      <c r="X97" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB97">
         <v>7</v>
       </c>
     </row>
@@ -5147,7 +5573,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -5159,19 +5585,19 @@
         <v>-44</v>
       </c>
       <c r="G98" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H98" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I98" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L98">
         <v>7</v>
@@ -5182,16 +5608,19 @@
       <c r="O98">
         <v>9</v>
       </c>
-      <c r="R98" t="s">
-        <v>56</v>
-      </c>
-      <c r="S98" t="s">
-        <v>39</v>
-      </c>
-      <c r="U98" t="s">
-        <v>37</v>
-      </c>
-      <c r="X98">
+      <c r="P98" t="s">
+        <v>104</v>
+      </c>
+      <c r="W98" t="s">
+        <v>64</v>
+      </c>
+      <c r="X98" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB98">
         <v>7</v>
       </c>
     </row>
@@ -5203,7 +5632,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D99">
         <v>4</v>
@@ -5215,15 +5644,15 @@
         <v>-44</v>
       </c>
       <c r="G99" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H99" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I99" t="s">
-        <v>54</v>
-      </c>
-      <c r="X99">
+        <v>61</v>
+      </c>
+      <c r="AB99">
         <v>7</v>
       </c>
     </row>
@@ -5235,7 +5664,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5247,19 +5676,19 @@
         <v>-31</v>
       </c>
       <c r="G100" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H100" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J100">
         <v>5</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L100">
         <v>6</v>
@@ -5270,25 +5699,31 @@
       <c r="O100">
         <v>2</v>
       </c>
-      <c r="Q100">
+      <c r="P100" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>39</v>
+      </c>
+      <c r="S100">
+        <v>3</v>
+      </c>
+      <c r="V100">
         <v>0</v>
       </c>
-      <c r="R100" t="s">
-        <v>37</v>
-      </c>
-      <c r="S100" t="s">
-        <v>78</v>
-      </c>
-      <c r="T100" t="s">
-        <v>76</v>
-      </c>
-      <c r="U100" t="s">
-        <v>37</v>
-      </c>
-      <c r="W100">
-        <v>3</v>
-      </c>
-      <c r="X100">
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB100">
         <v>6</v>
       </c>
     </row>
@@ -5300,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -5312,36 +5747,45 @@
         <v>-36</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H101" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I101" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J101">
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
-      <c r="R101" t="s">
-        <v>37</v>
-      </c>
-      <c r="S101" t="s">
+      <c r="P101" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>39</v>
+      </c>
+      <c r="S101">
+        <v>3</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y101" t="s">
         <v>99</v>
       </c>
-      <c r="T101" t="s">
-        <v>84</v>
-      </c>
-      <c r="U101" t="s">
-        <v>37</v>
-      </c>
-      <c r="X101">
+      <c r="Z101" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB101">
         <v>6</v>
       </c>
     </row>
@@ -5353,7 +5797,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -5365,19 +5809,19 @@
         <v>-39</v>
       </c>
       <c r="G102" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H102" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I102" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J102">
         <v>16</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L102">
         <v>7</v>
@@ -5388,22 +5832,31 @@
       <c r="O102">
         <v>4</v>
       </c>
+      <c r="P102" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>39</v>
+      </c>
       <c r="R102" t="s">
-        <v>34</v>
-      </c>
-      <c r="S102" t="s">
-        <v>48</v>
-      </c>
-      <c r="T102" t="s">
-        <v>100</v>
-      </c>
-      <c r="U102" t="s">
-        <v>34</v>
-      </c>
-      <c r="W102">
-        <v>3</v>
-      </c>
-      <c r="X102">
+        <v>115</v>
+      </c>
+      <c r="S102">
+        <v>3</v>
+      </c>
+      <c r="W102" t="s">
+        <v>40</v>
+      </c>
+      <c r="X102" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -5415,7 +5868,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -5427,19 +5880,19 @@
         <v>45</v>
       </c>
       <c r="G103" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H103" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I103" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L103">
         <v>7</v>
@@ -5450,22 +5903,31 @@
       <c r="O103">
         <v>3</v>
       </c>
+      <c r="P103" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>39</v>
+      </c>
       <c r="R103" t="s">
-        <v>34</v>
-      </c>
-      <c r="S103" t="s">
-        <v>48</v>
-      </c>
-      <c r="T103" t="s">
-        <v>52</v>
-      </c>
-      <c r="U103" t="s">
-        <v>37</v>
-      </c>
-      <c r="W103">
-        <v>3</v>
-      </c>
-      <c r="X103">
+        <v>121</v>
+      </c>
+      <c r="S103">
+        <v>3</v>
+      </c>
+      <c r="W103" t="s">
+        <v>40</v>
+      </c>
+      <c r="X103" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB103">
         <v>6</v>
       </c>
     </row>
@@ -5477,7 +5939,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5489,42 +5951,48 @@
         <v>45</v>
       </c>
       <c r="G104" t="s">
+        <v>40</v>
+      </c>
+      <c r="H104" t="s">
         <v>34</v>
       </c>
-      <c r="H104" t="s">
-        <v>30</v>
-      </c>
       <c r="I104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J104">
         <v>5</v>
       </c>
       <c r="K104" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L104">
         <v>7</v>
       </c>
       <c r="M104" t="s">
-        <v>33</v>
-      </c>
-      <c r="R104" t="s">
         <v>37</v>
       </c>
-      <c r="S104" t="s">
-        <v>101</v>
-      </c>
-      <c r="T104" t="s">
-        <v>102</v>
-      </c>
-      <c r="U104" t="s">
-        <v>37</v>
-      </c>
-      <c r="W104">
-        <v>3</v>
-      </c>
-      <c r="X104">
+      <c r="P104" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>39</v>
+      </c>
+      <c r="S104">
+        <v>3</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB104">
         <v>6</v>
       </c>
     </row>
@@ -5536,7 +6004,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>3</v>
@@ -5548,42 +6016,51 @@
         <v>40</v>
       </c>
       <c r="G105" t="s">
+        <v>40</v>
+      </c>
+      <c r="H105" t="s">
         <v>34</v>
       </c>
-      <c r="H105" t="s">
-        <v>30</v>
-      </c>
       <c r="I105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J105">
         <v>7</v>
       </c>
       <c r="K105" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L105">
         <v>8</v>
       </c>
       <c r="M105" t="s">
-        <v>38</v>
-      </c>
-      <c r="R105" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="P105" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>39</v>
       </c>
       <c r="S105" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T105" t="s">
-        <v>64</v>
-      </c>
-      <c r="U105" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="W105" t="s">
-        <v>59</v>
-      </c>
-      <c r="X105">
+        <v>43</v>
+      </c>
+      <c r="X105" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB105">
         <v>6</v>
       </c>
     </row>
@@ -5595,7 +6072,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5607,19 +6084,19 @@
         <v>33</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I106" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L106">
         <v>6</v>
@@ -5630,22 +6107,28 @@
       <c r="O106">
         <v>7</v>
       </c>
-      <c r="R106" t="s">
-        <v>34</v>
-      </c>
-      <c r="S106" t="s">
-        <v>51</v>
-      </c>
-      <c r="T106" t="s">
-        <v>84</v>
-      </c>
-      <c r="U106" t="s">
-        <v>34</v>
-      </c>
-      <c r="W106">
-        <v>6</v>
-      </c>
-      <c r="X106">
+      <c r="P106" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>39</v>
+      </c>
+      <c r="S106">
+        <v>6</v>
+      </c>
+      <c r="W106" t="s">
+        <v>40</v>
+      </c>
+      <c r="X106" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB106">
         <v>6</v>
       </c>
     </row>
@@ -5657,7 +6140,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5669,39 +6152,45 @@
         <v>33</v>
       </c>
       <c r="G107" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H107" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="J107">
         <v>-3</v>
       </c>
       <c r="K107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L107">
         <v>7</v>
       </c>
-      <c r="R107" t="s">
-        <v>34</v>
-      </c>
-      <c r="S107" t="s">
-        <v>99</v>
-      </c>
-      <c r="T107" t="s">
-        <v>104</v>
-      </c>
-      <c r="U107" t="s">
-        <v>37</v>
-      </c>
-      <c r="W107">
-        <v>3</v>
-      </c>
-      <c r="X107">
+      <c r="P107" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>39</v>
+      </c>
+      <c r="S107">
+        <v>3</v>
+      </c>
+      <c r="W107" t="s">
+        <v>40</v>
+      </c>
+      <c r="X107" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB107">
         <v>6</v>
       </c>
     </row>
@@ -5713,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5725,33 +6214,36 @@
         <v>-36</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J108">
         <v>3</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L108">
         <v>7</v>
       </c>
-      <c r="R108" t="s">
-        <v>37</v>
-      </c>
-      <c r="S108" t="s">
-        <v>69</v>
-      </c>
-      <c r="U108" t="s">
-        <v>37</v>
-      </c>
-      <c r="X108">
+      <c r="P108" t="s">
+        <v>63</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB108">
         <v>8</v>
       </c>
     </row>
@@ -5763,7 +6255,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5775,33 +6267,36 @@
         <v>-39</v>
       </c>
       <c r="G109" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J109">
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L109">
         <v>7</v>
       </c>
-      <c r="R109" t="s">
-        <v>56</v>
-      </c>
-      <c r="S109" t="s">
-        <v>39</v>
-      </c>
-      <c r="U109" t="s">
-        <v>37</v>
-      </c>
-      <c r="X109">
+      <c r="P109" t="s">
+        <v>63</v>
+      </c>
+      <c r="W109" t="s">
+        <v>64</v>
+      </c>
+      <c r="X109" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB109">
         <v>8</v>
       </c>
     </row>
@@ -5813,7 +6308,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5825,33 +6320,36 @@
         <v>-41</v>
       </c>
       <c r="G110" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I110" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J110">
         <v>-1</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L110">
         <v>7</v>
       </c>
-      <c r="R110" t="s">
-        <v>34</v>
-      </c>
-      <c r="S110" t="s">
-        <v>69</v>
-      </c>
-      <c r="U110" t="s">
-        <v>34</v>
-      </c>
-      <c r="X110">
+      <c r="P110" t="s">
+        <v>63</v>
+      </c>
+      <c r="W110" t="s">
+        <v>40</v>
+      </c>
+      <c r="X110" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110">
         <v>8</v>
       </c>
     </row>
@@ -5863,7 +6361,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -5875,18 +6373,18 @@
         <v>-40</v>
       </c>
       <c r="G111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H111" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I111" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q111">
+        <v>92</v>
+      </c>
+      <c r="V111">
         <v>15</v>
       </c>
-      <c r="X111">
+      <c r="AB111">
         <v>8</v>
       </c>
     </row>
@@ -5898,7 +6396,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5910,19 +6408,19 @@
         <v>-42</v>
       </c>
       <c r="G112" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H112" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J112">
         <v>7</v>
       </c>
       <c r="K112" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L112">
         <v>7</v>
@@ -5933,22 +6431,28 @@
       <c r="O112">
         <v>1</v>
       </c>
-      <c r="R112" t="s">
-        <v>37</v>
-      </c>
-      <c r="S112" t="s">
-        <v>44</v>
-      </c>
-      <c r="T112" t="s">
-        <v>45</v>
-      </c>
-      <c r="U112" t="s">
-        <v>34</v>
-      </c>
-      <c r="W112">
-        <v>3</v>
-      </c>
-      <c r="X112">
+      <c r="P112" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>39</v>
+      </c>
+      <c r="S112">
+        <v>3</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112">
         <v>7</v>
       </c>
     </row>
@@ -5960,7 +6464,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5972,19 +6476,19 @@
         <v>-49</v>
       </c>
       <c r="G113" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H113" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I113" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J113">
         <v>10</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L113">
         <v>6</v>
@@ -5995,22 +6499,28 @@
       <c r="O113">
         <v>3</v>
       </c>
-      <c r="R113" t="s">
-        <v>37</v>
-      </c>
-      <c r="S113" t="s">
-        <v>44</v>
-      </c>
-      <c r="T113" t="s">
-        <v>105</v>
-      </c>
-      <c r="U113" t="s">
-        <v>37</v>
+      <c r="P113" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>39</v>
+      </c>
+      <c r="S113">
+        <v>3</v>
       </c>
       <c r="W113" t="s">
-        <v>95</v>
-      </c>
-      <c r="X113">
+        <v>43</v>
+      </c>
+      <c r="X113" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB113">
         <v>7</v>
       </c>
     </row>
@@ -6022,7 +6532,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -6034,19 +6544,19 @@
         <v>41</v>
       </c>
       <c r="G114" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H114" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I114" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J114">
         <v>10</v>
       </c>
       <c r="K114" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L114">
         <v>6</v>
@@ -6057,22 +6567,31 @@
       <c r="O114">
         <v>4</v>
       </c>
+      <c r="P114" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>39</v>
+      </c>
       <c r="R114" t="s">
-        <v>34</v>
-      </c>
-      <c r="S114" t="s">
-        <v>44</v>
-      </c>
-      <c r="T114" t="s">
-        <v>45</v>
-      </c>
-      <c r="U114" t="s">
-        <v>34</v>
+        <v>128</v>
+      </c>
+      <c r="S114">
+        <v>3</v>
       </c>
       <c r="W114" t="s">
-        <v>95</v>
-      </c>
-      <c r="X114">
+        <v>40</v>
+      </c>
+      <c r="X114" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114">
         <v>7</v>
       </c>
     </row>
@@ -6084,7 +6603,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -6096,27 +6615,36 @@
         <v>31</v>
       </c>
       <c r="G115" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H115" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I115" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J115">
         <v>6</v>
       </c>
       <c r="K115" t="s">
-        <v>43</v>
-      </c>
-      <c r="R115" t="s">
-        <v>37</v>
-      </c>
-      <c r="S115" t="s">
-        <v>44</v>
-      </c>
-      <c r="X115">
+        <v>49</v>
+      </c>
+      <c r="P115" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>39</v>
+      </c>
+      <c r="S115">
+        <v>6</v>
+      </c>
+      <c r="W115" t="s">
+        <v>43</v>
+      </c>
+      <c r="X115" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB115">
         <v>7</v>
       </c>
     </row>
@@ -6128,7 +6656,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -6140,39 +6668,48 @@
         <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H116" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I116" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J116">
         <v>-4</v>
       </c>
       <c r="K116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L116">
         <v>5</v>
       </c>
+      <c r="P116" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>39</v>
+      </c>
       <c r="R116" t="s">
-        <v>37</v>
-      </c>
-      <c r="S116" t="s">
-        <v>44</v>
-      </c>
-      <c r="T116" t="s">
-        <v>76</v>
-      </c>
-      <c r="U116" t="s">
-        <v>37</v>
+        <v>121</v>
+      </c>
+      <c r="S116">
+        <v>3</v>
       </c>
       <c r="W116" t="s">
-        <v>95</v>
-      </c>
-      <c r="X116">
+        <v>43</v>
+      </c>
+      <c r="X116" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB116">
         <v>7</v>
       </c>
     </row>
@@ -6184,7 +6721,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>3</v>
@@ -6196,19 +6733,19 @@
         <v>29</v>
       </c>
       <c r="G117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H117" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I117" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L117">
         <v>6</v>
@@ -6219,22 +6756,31 @@
       <c r="O117">
         <v>4</v>
       </c>
+      <c r="P117" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>39</v>
+      </c>
       <c r="R117" t="s">
-        <v>34</v>
-      </c>
-      <c r="S117" t="s">
-        <v>78</v>
-      </c>
-      <c r="T117" t="s">
-        <v>45</v>
-      </c>
-      <c r="U117" t="s">
-        <v>37</v>
-      </c>
-      <c r="W117">
-        <v>3</v>
-      </c>
-      <c r="X117">
+        <v>129</v>
+      </c>
+      <c r="S117">
+        <v>3</v>
+      </c>
+      <c r="W117" t="s">
+        <v>40</v>
+      </c>
+      <c r="X117" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB117">
         <v>7</v>
       </c>
     </row>
@@ -6246,7 +6792,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -6258,27 +6804,33 @@
         <v>29</v>
       </c>
       <c r="G118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I118" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J118">
         <v>-5</v>
       </c>
       <c r="K118" t="s">
-        <v>32</v>
-      </c>
-      <c r="R118" t="s">
-        <v>34</v>
-      </c>
-      <c r="S118" t="s">
-        <v>48</v>
-      </c>
-      <c r="W118">
-        <v>6</v>
-      </c>
-      <c r="X118">
+        <v>36</v>
+      </c>
+      <c r="P118" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>39</v>
+      </c>
+      <c r="S118">
+        <v>6</v>
+      </c>
+      <c r="W118" t="s">
+        <v>40</v>
+      </c>
+      <c r="X118" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB118">
         <v>7</v>
       </c>
     </row>
@@ -6290,7 +6842,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -6302,19 +6854,19 @@
         <v>34</v>
       </c>
       <c r="G119" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H119" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I119" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L119">
         <v>6</v>
@@ -6325,22 +6877,31 @@
       <c r="O119">
         <v>1</v>
       </c>
+      <c r="P119" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>39</v>
+      </c>
       <c r="R119" t="s">
-        <v>37</v>
-      </c>
-      <c r="S119" t="s">
-        <v>78</v>
-      </c>
-      <c r="T119" t="s">
-        <v>76</v>
-      </c>
-      <c r="U119" t="s">
-        <v>34</v>
-      </c>
-      <c r="W119">
-        <v>6</v>
-      </c>
-      <c r="X119">
+        <v>98</v>
+      </c>
+      <c r="S119">
+        <v>6</v>
+      </c>
+      <c r="W119" t="s">
+        <v>43</v>
+      </c>
+      <c r="X119" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB119">
         <v>7</v>
       </c>
     </row>
@@ -6352,7 +6913,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -6364,33 +6925,36 @@
         <v>-34</v>
       </c>
       <c r="G120" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J120">
         <v>-3</v>
       </c>
       <c r="K120" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L120">
         <v>7</v>
       </c>
-      <c r="R120" t="s">
-        <v>37</v>
-      </c>
-      <c r="S120" t="s">
-        <v>68</v>
-      </c>
-      <c r="U120" t="s">
-        <v>34</v>
-      </c>
-      <c r="X120">
+      <c r="P120" t="s">
+        <v>29</v>
+      </c>
+      <c r="W120" t="s">
+        <v>43</v>
+      </c>
+      <c r="X120" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB120">
         <v>9</v>
       </c>
     </row>
@@ -6402,7 +6966,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6414,33 +6978,36 @@
         <v>-31</v>
       </c>
       <c r="G121" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J121">
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L121">
         <v>7</v>
       </c>
-      <c r="R121" t="s">
-        <v>56</v>
-      </c>
-      <c r="S121" t="s">
-        <v>39</v>
-      </c>
-      <c r="U121" t="s">
-        <v>37</v>
-      </c>
-      <c r="X121">
+      <c r="P121" t="s">
+        <v>63</v>
+      </c>
+      <c r="W121" t="s">
+        <v>64</v>
+      </c>
+      <c r="X121" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB121">
         <v>9</v>
       </c>
     </row>
